--- a/ExcelOperations/XLSSF/POI.xlsx
+++ b/ExcelOperations/XLSSF/POI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15750" windowHeight="6180" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15750" windowHeight="6180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,11 @@
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:P18"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Name</t>
   </si>
@@ -31,6 +30,9 @@
   </si>
   <si>
     <t>M2 - 147 Adarsh Nagar Bijapur</t>
+  </si>
+  <si>
+    <t>Naveen</t>
   </si>
 </sst>
 </file>
@@ -372,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
@@ -394,6 +396,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
